--- a/CHESS_Library/PSE_Templates/levee_pse.xlsx
+++ b/CHESS_Library/PSE_Templates/levee_pse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\CHESS_Library\PSE_Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\CHESS-Library\CHESS_Library\PSE_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33D56EC2-A096-4065-8B3F-D694B573083C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1C24F5-C8B7-4EE2-9D62-E1B2399F6A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{7BEFE9B2-63BD-46B7-80A0-2F6552BD29EB}"/>
+    <workbookView xWindow="1815" yWindow="1815" windowWidth="28800" windowHeight="15270" xr2:uid="{7BEFE9B2-63BD-46B7-80A0-2F6552BD29EB}"/>
   </bookViews>
   <sheets>
     <sheet name="levee_pse" sheetId="1" r:id="rId1"/>
@@ -1815,7 +1815,7 @@
         <v>47</v>
       </c>
       <c r="D12" s="18">
-        <v>176.45</v>
+        <v>0</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
